--- a/execl/monster.xlsx
+++ b/execl/monster.xlsx
@@ -1,185 +1,443 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="monster" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>表格备注</t>
+  </si>
+  <si>
+    <t>?&amp;\S</t>
+  </si>
+  <si>
+    <t>\S</t>
+  </si>
+  <si>
+    <t>xg、普通小怪
+bs、首领
+fg、飞行小怪
+jy、精英怪</t>
+  </si>
+  <si>
+    <t>默认普通（影响部分技能命中）
+0、普通单位
+1、空中单位</t>
+  </si>
+  <si>
+    <t>默认无标签
+1、近战
+2、远程</t>
+  </si>
+  <si>
+    <t>默认无标签（影响伤害值）
+人型：Hum
+野兽：Beast
+不死族：Undead
+暗系：Dark
+光系：Light</t>
+  </si>
+  <si>
+    <t>基础速度</t>
+  </si>
+  <si>
+    <t>限制最大移速，不配置不限制</t>
+  </si>
+  <si>
+    <t>怪物模型比例，
+万分比，默认10000</t>
+  </si>
+  <si>
+    <t>攻击技能，复合配置：</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>美术模型</t>
+  </si>
+  <si>
+    <t>基础生命</t>
+  </si>
+  <si>
+    <t>基础攻击</t>
+  </si>
+  <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
+    <t>怪物类型2</t>
+  </si>
+  <si>
+    <t>怪物类型3</t>
+  </si>
+  <si>
+    <t>怪物tag</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>最大速度</t>
+  </si>
+  <si>
+    <t>比例</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>battleModel</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>type1</t>
+  </si>
+  <si>
+    <t>type2</t>
+  </si>
+  <si>
+    <t>type3</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>maxMoveSpeed</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int64</t>
+  </si>
+  <si>
+    <t>monXG_01</t>
+  </si>
+  <si>
+    <t>怪物_01</t>
+  </si>
+  <si>
+    <t>xg</t>
+  </si>
+  <si>
+    <t>sk_ID</t>
+  </si>
+  <si>
+    <t>monXG_02</t>
+  </si>
+  <si>
+    <t>怪物_02</t>
+  </si>
+  <si>
+    <t>monXG_03</t>
+  </si>
+  <si>
+    <t>怪物_03</t>
+  </si>
+  <si>
+    <t>monXG_04</t>
+  </si>
+  <si>
+    <t>怪物_04</t>
+  </si>
+  <si>
+    <t>monXG_05</t>
+  </si>
+  <si>
+    <t>怪物_05</t>
+  </si>
+  <si>
+    <t>monJY_01</t>
+  </si>
+  <si>
+    <t>精英_01</t>
+  </si>
+  <si>
+    <t>jy</t>
+  </si>
+  <si>
+    <t>monJy_02</t>
+  </si>
+  <si>
+    <t>精英_02</t>
+  </si>
+  <si>
+    <t>monJy_03</t>
+  </si>
+  <si>
+    <t>精英_03</t>
+  </si>
+  <si>
+    <t>monBS_01</t>
+  </si>
+  <si>
+    <t>领主_01</t>
+  </si>
+  <si>
+    <t>bs</t>
+  </si>
+  <si>
+    <t>Hum|Dark</t>
+  </si>
+  <si>
+    <t>monBS_02</t>
+  </si>
+  <si>
+    <t>领主_02</t>
+  </si>
+  <si>
+    <t>Hum|Light</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -365,12 +623,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -472,161 +745,196 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="51">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -676,76 +984,15 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 7" xfId="50"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1244,585 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="14.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" style="1" customWidth="1"/>
+    <col min="3" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="19.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" ht="99.75" spans="1:13">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11">
+        <v>100</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11">
+        <v>500</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11">
+        <v>100</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11">
+        <v>500</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
+        <v>100</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11">
+        <v>500</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11">
+        <v>100</v>
+      </c>
+      <c r="E12" s="11">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11">
+        <v>500</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11">
+        <v>100</v>
+      </c>
+      <c r="E13" s="11">
+        <v>10</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11">
+        <v>1</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11">
+        <v>500</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11">
+        <v>500</v>
+      </c>
+      <c r="E14" s="11">
+        <v>50</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11">
+        <v>500</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11">
+        <v>500</v>
+      </c>
+      <c r="E15" s="11">
+        <v>50</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11">
+        <v>500</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11">
+        <v>500</v>
+      </c>
+      <c r="E16" s="11">
+        <v>50</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11">
+        <v>500</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="11">
+        <v>100</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="11">
+        <v>500</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="11">
+        <v>100</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="11">
+        <v>500</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>